--- a/qc/spreadsheets/ugr_qc.xlsx
+++ b/qc/spreadsheets/ugr_qc.xlsx
@@ -7583,19 +7583,19 @@
         <v>0.1275073178998027</v>
       </c>
       <c r="H78" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K78" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.3125</v>
       </c>
       <c r="L78" t="n">
-        <v>99.84191508581752</v>
+        <v>99.84590041978851</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>

--- a/qc/spreadsheets/ugr_qc.xlsx
+++ b/qc/spreadsheets/ugr_qc.xlsx
@@ -464,8 +464,8 @@
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="45" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
     <col width="45" customWidth="1" min="22" max="22"/>
     <col width="45" customWidth="1" min="23" max="23"/>
     <col width="45" customWidth="1" min="24" max="24"/>
@@ -29780,6 +29780,18 @@
       <c r="G321" t="n">
         <v>0.1717587799884509</v>
       </c>
+      <c r="H321" t="n">
+        <v>43</v>
+      </c>
+      <c r="I321" t="n">
+        <v>13</v>
+      </c>
+      <c r="J321" t="n">
+        <v>30</v>
+      </c>
+      <c r="K321" t="n">
+        <v>0.6976744186046512</v>
+      </c>
       <c r="L321" t="n">
         <v>99.43541102077687</v>
       </c>
@@ -29789,6 +29801,9 @@
       <c r="N321" t="b">
         <v>0</v>
       </c>
+      <c r="O321" t="b">
+        <v>0</v>
+      </c>
       <c r="P321" t="b">
         <v>0</v>
       </c>
@@ -29796,16 +29811,11 @@
         <v>0</v>
       </c>
       <c r="S321" t="b">
-        <v>0</v>
-      </c>
-      <c r="T321" t="inlineStr">
-        <is>
-          <t>tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V321" t="inlineStr">
@@ -29816,6 +29826,11 @@
       <c r="W321" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-11083/ses-02/func/sub-11083_ses-02_task-ugr_run-1_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-11083/ses-02/sub-11083_ses-02_task-ugr_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y321" t="inlineStr">
@@ -29856,6 +29871,18 @@
       <c r="G322" t="n">
         <v>0.175058148647325</v>
       </c>
+      <c r="H322" t="n">
+        <v>55</v>
+      </c>
+      <c r="I322" t="n">
+        <v>17</v>
+      </c>
+      <c r="J322" t="n">
+        <v>38</v>
+      </c>
+      <c r="K322" t="n">
+        <v>0.6909090909090909</v>
+      </c>
       <c r="L322" t="n">
         <v>99.52308836813859</v>
       </c>
@@ -29865,6 +29892,9 @@
       <c r="N322" t="b">
         <v>0</v>
       </c>
+      <c r="O322" t="b">
+        <v>0</v>
+      </c>
       <c r="P322" t="b">
         <v>0</v>
       </c>
@@ -29872,16 +29902,11 @@
         <v>0</v>
       </c>
       <c r="S322" t="b">
-        <v>0</v>
-      </c>
-      <c r="T322" t="inlineStr">
-        <is>
-          <t>tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U322" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V322" t="inlineStr">
@@ -29892,6 +29917,11 @@
       <c r="W322" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-11083/ses-02/func/sub-11083_ses-02_task-ugr_run-2_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-11083/ses-02/sub-11083_ses-02_task-ugr_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y322" t="inlineStr">
@@ -30114,6 +30144,18 @@
       <c r="G325" t="n">
         <v>0.1470717139164353</v>
       </c>
+      <c r="H325" t="n">
+        <v>17</v>
+      </c>
+      <c r="I325" t="n">
+        <v>8</v>
+      </c>
+      <c r="J325" t="n">
+        <v>9</v>
+      </c>
+      <c r="K325" t="n">
+        <v>0.5294117647058824</v>
+      </c>
       <c r="L325" t="n">
         <v>99.86051331101547</v>
       </c>
@@ -30123,6 +30165,9 @@
       <c r="N325" t="b">
         <v>0</v>
       </c>
+      <c r="O325" t="b">
+        <v>0</v>
+      </c>
       <c r="P325" t="b">
         <v>0</v>
       </c>
@@ -30130,16 +30175,11 @@
         <v>0</v>
       </c>
       <c r="S325" t="b">
-        <v>0</v>
-      </c>
-      <c r="T325" t="inlineStr">
-        <is>
-          <t>tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U325" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V325" t="inlineStr">
@@ -30150,6 +30190,11 @@
       <c r="W325" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-11084/ses-02/func/sub-11084_ses-02_task-ugr_run-1_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-11084/ses-02/sub-11084_ses-02_task-ugr_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y325" t="inlineStr">
@@ -30190,6 +30235,18 @@
       <c r="G326" t="n">
         <v>0.1458920415741344</v>
       </c>
+      <c r="H326" t="n">
+        <v>20</v>
+      </c>
+      <c r="I326" t="n">
+        <v>9</v>
+      </c>
+      <c r="J326" t="n">
+        <v>11</v>
+      </c>
+      <c r="K326" t="n">
+        <v>0.55</v>
+      </c>
       <c r="L326" t="n">
         <v>99.87512620224241</v>
       </c>
@@ -30199,6 +30256,9 @@
       <c r="N326" t="b">
         <v>0</v>
       </c>
+      <c r="O326" t="b">
+        <v>0</v>
+      </c>
       <c r="P326" t="b">
         <v>0</v>
       </c>
@@ -30206,16 +30266,11 @@
         <v>0</v>
       </c>
       <c r="S326" t="b">
-        <v>0</v>
-      </c>
-      <c r="T326" t="inlineStr">
-        <is>
-          <t>tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V326" t="inlineStr">
@@ -30226,6 +30281,11 @@
       <c r="W326" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-11084/ses-02/func/sub-11084_ses-02_task-ugr_run-2_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-11084/ses-02/sub-11084_ses-02_task-ugr_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y326" t="inlineStr">
@@ -30640,6 +30700,18 @@
       <c r="G331" t="n">
         <v>0.1300364090015847</v>
       </c>
+      <c r="H331" t="n">
+        <v>17</v>
+      </c>
+      <c r="I331" t="n">
+        <v>8</v>
+      </c>
+      <c r="J331" t="n">
+        <v>9</v>
+      </c>
+      <c r="K331" t="n">
+        <v>0.5294117647058824</v>
+      </c>
       <c r="L331" t="n">
         <v>99.78612041022372</v>
       </c>
@@ -30649,6 +30721,9 @@
       <c r="N331" t="b">
         <v>0</v>
       </c>
+      <c r="O331" t="b">
+        <v>0</v>
+      </c>
       <c r="P331" t="b">
         <v>0</v>
       </c>
@@ -30656,16 +30731,11 @@
         <v>0</v>
       </c>
       <c r="S331" t="b">
-        <v>0</v>
-      </c>
-      <c r="T331" t="inlineStr">
-        <is>
-          <t>tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U331" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V331" t="inlineStr">
@@ -30676,6 +30746,11 @@
       <c r="W331" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-11110/ses-02/func/sub-11110_ses-02_task-ugr_run-1_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-11110/ses-02/sub-11110_ses-02_task-ugr_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y331" t="inlineStr">
@@ -30716,6 +30791,18 @@
       <c r="G332" t="n">
         <v>0.1845495182511284</v>
       </c>
+      <c r="H332" t="n">
+        <v>29</v>
+      </c>
+      <c r="I332" t="n">
+        <v>16</v>
+      </c>
+      <c r="J332" t="n">
+        <v>13</v>
+      </c>
+      <c r="K332" t="n">
+        <v>0.4482758620689655</v>
+      </c>
       <c r="L332" t="n">
         <v>99.83128752856156</v>
       </c>
@@ -30725,6 +30812,9 @@
       <c r="N332" t="b">
         <v>0</v>
       </c>
+      <c r="O332" t="b">
+        <v>0</v>
+      </c>
       <c r="P332" t="b">
         <v>0</v>
       </c>
@@ -30732,16 +30822,11 @@
         <v>0</v>
       </c>
       <c r="S332" t="b">
-        <v>0</v>
-      </c>
-      <c r="T332" t="inlineStr">
-        <is>
-          <t>tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U332" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V332" t="inlineStr">
@@ -30752,6 +30837,11 @@
       <c r="W332" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-11110/ses-02/func/sub-11110_ses-02_task-ugr_run-2_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-11110/ses-02/sub-11110_ses-02_task-ugr_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y332" t="inlineStr">
@@ -31525,6 +31615,18 @@
       <c r="G341" t="n">
         <v>0.1584327384144076</v>
       </c>
+      <c r="H341" t="n">
+        <v>31</v>
+      </c>
+      <c r="I341" t="n">
+        <v>18</v>
+      </c>
+      <c r="J341" t="n">
+        <v>13</v>
+      </c>
+      <c r="K341" t="n">
+        <v>0.4193548387096774</v>
+      </c>
       <c r="L341" t="n">
         <v>99.83128752856156</v>
       </c>
@@ -31534,6 +31636,9 @@
       <c r="N341" t="b">
         <v>0</v>
       </c>
+      <c r="O341" t="b">
+        <v>0</v>
+      </c>
       <c r="P341" t="b">
         <v>0</v>
       </c>
@@ -31541,16 +31646,11 @@
         <v>0</v>
       </c>
       <c r="S341" t="b">
-        <v>0</v>
-      </c>
-      <c r="T341" t="inlineStr">
-        <is>
-          <t>tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U341" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V341" t="inlineStr">
@@ -31561,6 +31661,11 @@
       <c r="W341" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-11120/ses-02/func/sub-11120_ses-02_task-ugr_run-1_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-11120/ses-02/sub-11120_ses-02_task-ugr_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y341" t="inlineStr">
@@ -31601,6 +31706,18 @@
       <c r="G342" t="n">
         <v>0.1654602049495668</v>
       </c>
+      <c r="H342" t="n">
+        <v>33</v>
+      </c>
+      <c r="I342" t="n">
+        <v>22</v>
+      </c>
+      <c r="J342" t="n">
+        <v>11</v>
+      </c>
+      <c r="K342" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="L342" t="n">
         <v>99.77814974228174</v>
       </c>
@@ -31610,6 +31727,9 @@
       <c r="N342" t="b">
         <v>0</v>
       </c>
+      <c r="O342" t="b">
+        <v>0</v>
+      </c>
       <c r="P342" t="b">
         <v>0</v>
       </c>
@@ -31617,16 +31737,11 @@
         <v>0</v>
       </c>
       <c r="S342" t="b">
-        <v>0</v>
-      </c>
-      <c r="T342" t="inlineStr">
-        <is>
-          <t>tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U342" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V342" t="inlineStr">
@@ -31637,6 +31752,11 @@
       <c r="W342" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-11120/ses-02/func/sub-11120_ses-02_task-ugr_run-2_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-11120/ses-02/sub-11120_ses-02_task-ugr_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y342" t="inlineStr">
@@ -33689,6 +33809,18 @@
       <c r="G365" t="n">
         <v>0.129915666173661</v>
       </c>
+      <c r="H365" t="n">
+        <v>19</v>
+      </c>
+      <c r="I365" t="n">
+        <v>11</v>
+      </c>
+      <c r="J365" t="n">
+        <v>8</v>
+      </c>
+      <c r="K365" t="n">
+        <v>0.4210526315789473</v>
+      </c>
       <c r="L365" t="n">
         <v>99.67187416972209</v>
       </c>
@@ -33698,6 +33830,9 @@
       <c r="N365" t="b">
         <v>0</v>
       </c>
+      <c r="O365" t="b">
+        <v>0</v>
+      </c>
       <c r="P365" t="b">
         <v>0</v>
       </c>
@@ -33705,16 +33840,11 @@
         <v>0</v>
       </c>
       <c r="S365" t="b">
-        <v>0</v>
-      </c>
-      <c r="T365" t="inlineStr">
-        <is>
-          <t>tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U365" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V365" t="inlineStr">
@@ -33725,6 +33855,11 @@
       <c r="W365" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-11193/ses-02/func/sub-11193_ses-02_task-ugr_run-1_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-11193/ses-02/sub-11193_ses-02_task-ugr_run-1_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y365" t="inlineStr">
@@ -33765,6 +33900,18 @@
       <c r="G366" t="n">
         <v>0.115895385020239</v>
       </c>
+      <c r="H366" t="n">
+        <v>15</v>
+      </c>
+      <c r="I366" t="n">
+        <v>5</v>
+      </c>
+      <c r="J366" t="n">
+        <v>10</v>
+      </c>
+      <c r="K366" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="L366" t="n">
         <v>99.698443062862</v>
       </c>
@@ -33774,6 +33921,9 @@
       <c r="N366" t="b">
         <v>0</v>
       </c>
+      <c r="O366" t="b">
+        <v>0</v>
+      </c>
       <c r="P366" t="b">
         <v>0</v>
       </c>
@@ -33781,16 +33931,11 @@
         <v>0</v>
       </c>
       <c r="S366" t="b">
-        <v>0</v>
-      </c>
-      <c r="T366" t="inlineStr">
-        <is>
-          <t>tedana_rejected_components:missing_tedana_metrics</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U366" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="V366" t="inlineStr">
@@ -33801,6 +33946,11 @@
       <c r="W366" t="inlineStr">
         <is>
           <t>derivatives/mriqc/sub-11193/ses-02/func/sub-11193_ses-02_task-ugr_run-2_echo-2_part-mag_bold.json</t>
+        </is>
+      </c>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>derivatives/tedana/sub-11193/ses-02/sub-11193_ses-02_task-ugr_run-2_desc-tedana_metrics.tsv</t>
         </is>
       </c>
       <c r="Y366" t="inlineStr">
@@ -67352,22 +67502,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="H8" t="n">
         <v>34</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.5</v>
+        <v>-14.75</v>
       </c>
       <c r="K8" t="n">
-        <v>59.5</v>
+        <v>63.25</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
